--- a/artfynd/A 22203-2023 artfynd.xlsx
+++ b/artfynd/A 22203-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3391,6 +3391,783 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>113702286</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97398</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hössjökälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>735961</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7082963</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>113702291</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97398</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hössjökälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>736012</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7082896</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>113702288</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97398</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hössjökälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>735927</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7082921</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>113702289</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97398</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hössjökälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>735942</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7082940</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>113702622</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90412</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>658</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hössjökälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>736082</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7082922</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>113702292</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97398</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hössjökälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>736028</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7082840</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>113702290</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97398</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hössjökälen, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>735942</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7082906</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22203-2023 artfynd.xlsx
+++ b/artfynd/A 22203-2023 artfynd.xlsx
@@ -3393,10 +3393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113702286</v>
+        <v>113702622</v>
       </c>
       <c r="B26" t="n">
-        <v>97398</v>
+        <v>90412</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3405,25 +3405,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735961</v>
+        <v>736082</v>
       </c>
       <c r="R26" t="n">
-        <v>7082963</v>
+        <v>7082922</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3480,12 +3480,12 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AS26" t="inlineStr">
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr">
         <is>
           <t>Jessica  Åström</t>
         </is>
       </c>
-      <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113702291</v>
+        <v>113702288</v>
       </c>
       <c r="B27" t="n">
         <v>97398</v>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736012</v>
+        <v>735927</v>
       </c>
       <c r="R27" t="n">
-        <v>7082896</v>
+        <v>7082921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113702288</v>
+        <v>113702290</v>
       </c>
       <c r="B28" t="n">
         <v>97398</v>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735927</v>
+        <v>735942</v>
       </c>
       <c r="R28" t="n">
-        <v>7082921</v>
+        <v>7082906</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113702289</v>
+        <v>113702286</v>
       </c>
       <c r="B29" t="n">
         <v>97398</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735942</v>
+        <v>735961</v>
       </c>
       <c r="R29" t="n">
-        <v>7082940</v>
+        <v>7082963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113702622</v>
+        <v>113702291</v>
       </c>
       <c r="B30" t="n">
-        <v>90412</v>
+        <v>97398</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3849,25 +3849,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736082</v>
+        <v>736012</v>
       </c>
       <c r="R30" t="n">
-        <v>7082922</v>
+        <v>7082896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3924,12 +3924,12 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>Jessica  Åström</t>
-        </is>
-      </c>
       <c r="AW30" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113702292</v>
+        <v>113702289</v>
       </c>
       <c r="B31" t="n">
         <v>97398</v>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736028</v>
+        <v>735942</v>
       </c>
       <c r="R31" t="n">
-        <v>7082840</v>
+        <v>7082940</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113702290</v>
+        <v>113702292</v>
       </c>
       <c r="B32" t="n">
         <v>97398</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735942</v>
+        <v>736028</v>
       </c>
       <c r="R32" t="n">
-        <v>7082906</v>
+        <v>7082840</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 22203-2023 artfynd.xlsx
+++ b/artfynd/A 22203-2023 artfynd.xlsx
@@ -3396,7 +3396,7 @@
         <v>113702622</v>
       </c>
       <c r="B26" t="n">
-        <v>90412</v>
+        <v>90416</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113702288</v>
+        <v>113702292</v>
       </c>
       <c r="B27" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735927</v>
+        <v>736028</v>
       </c>
       <c r="R27" t="n">
-        <v>7082921</v>
+        <v>7082840</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113702290</v>
+        <v>113702291</v>
       </c>
       <c r="B28" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735942</v>
+        <v>736012</v>
       </c>
       <c r="R28" t="n">
-        <v>7082906</v>
+        <v>7082896</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113702286</v>
+        <v>113702288</v>
       </c>
       <c r="B29" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735961</v>
+        <v>735927</v>
       </c>
       <c r="R29" t="n">
-        <v>7082963</v>
+        <v>7082921</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113702291</v>
+        <v>113702286</v>
       </c>
       <c r="B30" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736012</v>
+        <v>735961</v>
       </c>
       <c r="R30" t="n">
-        <v>7082896</v>
+        <v>7082963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3951,7 +3951,7 @@
         <v>113702289</v>
       </c>
       <c r="B31" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113702292</v>
+        <v>113702290</v>
       </c>
       <c r="B32" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736028</v>
+        <v>735942</v>
       </c>
       <c r="R32" t="n">
-        <v>7082840</v>
+        <v>7082906</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 22203-2023 artfynd.xlsx
+++ b/artfynd/A 22203-2023 artfynd.xlsx
@@ -3393,10 +3393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113702622</v>
+        <v>113702286</v>
       </c>
       <c r="B26" t="n">
-        <v>90416</v>
+        <v>97402</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3405,25 +3405,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736082</v>
+        <v>735961</v>
       </c>
       <c r="R26" t="n">
-        <v>7082922</v>
+        <v>7082963</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3480,12 +3480,12 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
       <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>Jessica  Åström</t>
-        </is>
-      </c>
       <c r="AW26" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113702292</v>
+        <v>113702290</v>
       </c>
       <c r="B27" t="n">
         <v>97402</v>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736028</v>
+        <v>735942</v>
       </c>
       <c r="R27" t="n">
-        <v>7082840</v>
+        <v>7082906</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113702291</v>
+        <v>113702289</v>
       </c>
       <c r="B28" t="n">
         <v>97402</v>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736012</v>
+        <v>735942</v>
       </c>
       <c r="R28" t="n">
-        <v>7082896</v>
+        <v>7082940</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113702288</v>
+        <v>113702622</v>
       </c>
       <c r="B29" t="n">
-        <v>97402</v>
+        <v>90416</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3738,25 +3738,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735927</v>
+        <v>736082</v>
       </c>
       <c r="R29" t="n">
-        <v>7082921</v>
+        <v>7082922</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3813,12 +3813,12 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AS29" t="inlineStr">
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr">
         <is>
           <t>Jessica  Åström</t>
         </is>
       </c>
-      <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113702286</v>
+        <v>113702291</v>
       </c>
       <c r="B30" t="n">
         <v>97402</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735961</v>
+        <v>736012</v>
       </c>
       <c r="R30" t="n">
-        <v>7082963</v>
+        <v>7082896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113702289</v>
+        <v>113702292</v>
       </c>
       <c r="B31" t="n">
         <v>97402</v>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735942</v>
+        <v>736028</v>
       </c>
       <c r="R31" t="n">
-        <v>7082940</v>
+        <v>7082840</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113702290</v>
+        <v>113702288</v>
       </c>
       <c r="B32" t="n">
         <v>97402</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735942</v>
+        <v>735927</v>
       </c>
       <c r="R32" t="n">
-        <v>7082906</v>
+        <v>7082921</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 22203-2023 artfynd.xlsx
+++ b/artfynd/A 22203-2023 artfynd.xlsx
@@ -3393,7 +3393,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113702286</v>
+        <v>113702290</v>
       </c>
       <c r="B26" t="n">
         <v>97402</v>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735961</v>
+        <v>735942</v>
       </c>
       <c r="R26" t="n">
-        <v>7082963</v>
+        <v>7082906</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113702290</v>
+        <v>113702288</v>
       </c>
       <c r="B27" t="n">
         <v>97402</v>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735942</v>
+        <v>735927</v>
       </c>
       <c r="R27" t="n">
-        <v>7082906</v>
+        <v>7082921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113702289</v>
+        <v>113702286</v>
       </c>
       <c r="B28" t="n">
         <v>97402</v>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735942</v>
+        <v>735961</v>
       </c>
       <c r="R28" t="n">
-        <v>7082940</v>
+        <v>7082963</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113702291</v>
+        <v>113702292</v>
       </c>
       <c r="B30" t="n">
         <v>97402</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736012</v>
+        <v>736028</v>
       </c>
       <c r="R30" t="n">
-        <v>7082896</v>
+        <v>7082840</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113702292</v>
+        <v>113702289</v>
       </c>
       <c r="B31" t="n">
         <v>97402</v>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736028</v>
+        <v>735942</v>
       </c>
       <c r="R31" t="n">
-        <v>7082840</v>
+        <v>7082940</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113702288</v>
+        <v>113702291</v>
       </c>
       <c r="B32" t="n">
         <v>97402</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735927</v>
+        <v>736012</v>
       </c>
       <c r="R32" t="n">
-        <v>7082921</v>
+        <v>7082896</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 22203-2023 artfynd.xlsx
+++ b/artfynd/A 22203-2023 artfynd.xlsx
@@ -3615,7 +3615,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113702286</v>
+        <v>113702291</v>
       </c>
       <c r="B28" t="n">
         <v>97402</v>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735961</v>
+        <v>736012</v>
       </c>
       <c r="R28" t="n">
-        <v>7082963</v>
+        <v>7082896</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113702291</v>
+        <v>113702286</v>
       </c>
       <c r="B32" t="n">
         <v>97402</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736012</v>
+        <v>735961</v>
       </c>
       <c r="R32" t="n">
-        <v>7082896</v>
+        <v>7082963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 22203-2023 artfynd.xlsx
+++ b/artfynd/A 22203-2023 artfynd.xlsx
@@ -3393,10 +3393,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113702290</v>
+        <v>113702622</v>
       </c>
       <c r="B26" t="n">
-        <v>97402</v>
+        <v>90416</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3405,25 +3405,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735942</v>
+        <v>736082</v>
       </c>
       <c r="R26" t="n">
-        <v>7082906</v>
+        <v>7082922</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3480,12 +3480,12 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AS26" t="inlineStr">
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr">
         <is>
           <t>Jessica  Åström</t>
         </is>
       </c>
-      <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113702288</v>
+        <v>113702286</v>
       </c>
       <c r="B27" t="n">
         <v>97402</v>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735927</v>
+        <v>735961</v>
       </c>
       <c r="R27" t="n">
-        <v>7082921</v>
+        <v>7082963</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113702291</v>
+        <v>113702290</v>
       </c>
       <c r="B28" t="n">
         <v>97402</v>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736012</v>
+        <v>735942</v>
       </c>
       <c r="R28" t="n">
-        <v>7082896</v>
+        <v>7082906</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113702622</v>
+        <v>113702289</v>
       </c>
       <c r="B29" t="n">
-        <v>90416</v>
+        <v>97402</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3738,25 +3738,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736082</v>
+        <v>735942</v>
       </c>
       <c r="R29" t="n">
-        <v>7082922</v>
+        <v>7082940</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3813,12 +3813,12 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>Jessica  Åström</t>
-        </is>
-      </c>
       <c r="AW29" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113702289</v>
+        <v>113702291</v>
       </c>
       <c r="B31" t="n">
         <v>97402</v>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735942</v>
+        <v>736012</v>
       </c>
       <c r="R31" t="n">
-        <v>7082940</v>
+        <v>7082896</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113702286</v>
+        <v>113702288</v>
       </c>
       <c r="B32" t="n">
         <v>97402</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735961</v>
+        <v>735927</v>
       </c>
       <c r="R32" t="n">
-        <v>7082963</v>
+        <v>7082921</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 22203-2023 artfynd.xlsx
+++ b/artfynd/A 22203-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
